--- a/output/yearly_total_coral_cover_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_97_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.269916608155458</v>
+        <v>1.267403334032586</v>
       </c>
       <c r="C3" t="n">
-        <v>4.588597358173258</v>
+        <v>4.669493369003195</v>
       </c>
       <c r="D3" t="n">
-        <v>6.134602794814993</v>
+        <v>6.049779793168068</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99311676114371</v>
+        <v>11.98667649620385</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.423817737921719</v>
+        <v>1.415896139060155</v>
       </c>
       <c r="C4" t="n">
-        <v>5.015242938562645</v>
+        <v>5.284267230065176</v>
       </c>
       <c r="D4" t="n">
-        <v>6.392537429840514</v>
+        <v>6.303463590647342</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83159810632488</v>
+        <v>13.00362695977267</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.628694150622027</v>
+        <v>1.606023643718104</v>
       </c>
       <c r="C5" t="n">
-        <v>5.535388563592996</v>
+        <v>6.092315909873149</v>
       </c>
       <c r="D5" t="n">
-        <v>6.799321954010204</v>
+        <v>6.579197689694923</v>
       </c>
       <c r="E5" t="n">
-        <v>13.96340466822523</v>
+        <v>14.27753724328618</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.861880529182701</v>
+        <v>1.826020022648074</v>
       </c>
       <c r="C6" t="n">
-        <v>6.179014214749587</v>
+        <v>7.084271016723648</v>
       </c>
       <c r="D6" t="n">
-        <v>7.28276133390681</v>
+        <v>6.934930478785168</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3236560778391</v>
+        <v>15.84522151815689</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.12760356659359</v>
+        <v>2.06398550495769</v>
       </c>
       <c r="C7" t="n">
-        <v>6.946552231739313</v>
+        <v>8.217105188721604</v>
       </c>
       <c r="D7" t="n">
-        <v>7.750361603537943</v>
+        <v>7.338036685129417</v>
       </c>
       <c r="E7" t="n">
-        <v>16.82451740187085</v>
+        <v>17.61912737880871</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.355413341816683</v>
+        <v>1.274790296598106</v>
       </c>
       <c r="C8" t="n">
-        <v>4.609155997375901</v>
+        <v>5.802116048182052</v>
       </c>
       <c r="D8" t="n">
-        <v>6.01044305161663</v>
+        <v>5.562072433525385</v>
       </c>
       <c r="E8" t="n">
-        <v>11.97501239080921</v>
+        <v>12.63897877830554</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.737339080885723</v>
+        <v>1.590630436167326</v>
       </c>
       <c r="C9" t="n">
-        <v>5.554349516057105</v>
+        <v>7.152213305953605</v>
       </c>
       <c r="D9" t="n">
-        <v>6.569117288206438</v>
+        <v>6.023898025320944</v>
       </c>
       <c r="E9" t="n">
-        <v>13.86080588514927</v>
+        <v>14.76674176744188</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.15142579418456</v>
+        <v>1.923886800472846</v>
       </c>
       <c r="C10" t="n">
-        <v>6.676115471026391</v>
+        <v>8.652909542875539</v>
       </c>
       <c r="D10" t="n">
-        <v>7.113934637180209</v>
+        <v>6.524373109177526</v>
       </c>
       <c r="E10" t="n">
-        <v>15.94147590239116</v>
+        <v>17.10116945252591</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.585964518708542</v>
+        <v>2.263253797395729</v>
       </c>
       <c r="C11" t="n">
-        <v>7.914322211648259</v>
+        <v>10.27108186263754</v>
       </c>
       <c r="D11" t="n">
-        <v>7.806800859599439</v>
+        <v>6.983398584643968</v>
       </c>
       <c r="E11" t="n">
-        <v>18.30708758995624</v>
+        <v>19.51773424467724</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.019462585366949</v>
+        <v>2.598143785716809</v>
       </c>
       <c r="C12" t="n">
-        <v>9.27174444651939</v>
+        <v>11.99042653893419</v>
       </c>
       <c r="D12" t="n">
-        <v>8.370402198463475</v>
+        <v>7.479157448509535</v>
       </c>
       <c r="E12" t="n">
-        <v>20.66160923034981</v>
+        <v>22.06772777316054</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.436283600579647</v>
+        <v>2.906842613183938</v>
       </c>
       <c r="C13" t="n">
-        <v>10.73702252674607</v>
+        <v>13.73122430540141</v>
       </c>
       <c r="D13" t="n">
-        <v>8.992874879454192</v>
+        <v>7.901811857309659</v>
       </c>
       <c r="E13" t="n">
-        <v>23.1661810067799</v>
+        <v>24.53987877589501</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.962719827807266</v>
+        <v>1.66814642914801</v>
       </c>
       <c r="C14" t="n">
-        <v>7.636524517483815</v>
+        <v>9.662812509141062</v>
       </c>
       <c r="D14" t="n">
-        <v>6.797257857554343</v>
+        <v>6.020057287487357</v>
       </c>
       <c r="E14" t="n">
-        <v>16.39650220284543</v>
+        <v>17.35101622577643</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.034200878153476</v>
+        <v>1.698266448714302</v>
       </c>
       <c r="C15" t="n">
-        <v>8.330050730717845</v>
+        <v>10.4707025124428</v>
       </c>
       <c r="D15" t="n">
-        <v>6.896463463068485</v>
+        <v>6.00794252081695</v>
       </c>
       <c r="E15" t="n">
-        <v>17.26071507193981</v>
+        <v>18.17691148197406</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.376438127853914</v>
+        <v>1.952372207004504</v>
       </c>
       <c r="C16" t="n">
-        <v>9.91328580092555</v>
+        <v>12.38224383242768</v>
       </c>
       <c r="D16" t="n">
-        <v>7.511891646429683</v>
+        <v>6.445026416224674</v>
       </c>
       <c r="E16" t="n">
-        <v>19.80161557520915</v>
+        <v>20.77964245565686</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.916204621580052</v>
+        <v>1.555235625682585</v>
       </c>
       <c r="C17" t="n">
-        <v>9.251116609365161</v>
+        <v>11.38816537701553</v>
       </c>
       <c r="D17" t="n">
-        <v>7.04080001054685</v>
+        <v>5.969546368103859</v>
       </c>
       <c r="E17" t="n">
-        <v>18.20812124149206</v>
+        <v>18.91294737080198</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.193931229634432</v>
+        <v>1.763915917697287</v>
       </c>
       <c r="C18" t="n">
-        <v>10.82038140974143</v>
+        <v>13.29113603954234</v>
       </c>
       <c r="D18" t="n">
-        <v>7.51773304526995</v>
+        <v>6.362539974113856</v>
       </c>
       <c r="E18" t="n">
-        <v>20.53204568464582</v>
+        <v>21.41759193135348</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.207901499465864</v>
+        <v>1.756582262346563</v>
       </c>
       <c r="C19" t="n">
-        <v>11.59715001081855</v>
+        <v>14.22558313939854</v>
       </c>
       <c r="D19" t="n">
-        <v>7.650936573782158</v>
+        <v>6.43563109069503</v>
       </c>
       <c r="E19" t="n">
-        <v>21.45598808406658</v>
+        <v>22.41779649244013</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.46301845789144</v>
+        <v>1.940915211295944</v>
       </c>
       <c r="C20" t="n">
-        <v>13.40877886694224</v>
+        <v>16.29598105540759</v>
       </c>
       <c r="D20" t="n">
-        <v>8.202413711688719</v>
+        <v>6.861100910761515</v>
       </c>
       <c r="E20" t="n">
-        <v>24.07421103652239</v>
+        <v>25.09799717746505</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.464139256205523</v>
+        <v>1.14574865824124</v>
       </c>
       <c r="C21" t="n">
-        <v>9.905520176584959</v>
+        <v>11.94504212729545</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880824222139832</v>
+        <v>5.720899127049268</v>
       </c>
       <c r="E21" t="n">
-        <v>18.25048365493031</v>
+        <v>18.81168991258596</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_97_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.267403334032586</v>
+        <v>1.254562074061037</v>
       </c>
       <c r="C3" t="n">
-        <v>4.669493369003195</v>
+        <v>4.607937787946921</v>
       </c>
       <c r="D3" t="n">
-        <v>6.049779793168068</v>
+        <v>6.161973920809394</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98667649620385</v>
+        <v>12.02447378281735</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.415896139060155</v>
+        <v>1.387418974196815</v>
       </c>
       <c r="C4" t="n">
-        <v>5.284267230065176</v>
+        <v>5.079440726713631</v>
       </c>
       <c r="D4" t="n">
-        <v>6.303463590647342</v>
+        <v>6.442547025385615</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00362695977267</v>
+        <v>12.90940672629606</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.606023643718104</v>
+        <v>1.566587460014959</v>
       </c>
       <c r="C5" t="n">
-        <v>6.092315909873149</v>
+        <v>5.651333810147318</v>
       </c>
       <c r="D5" t="n">
-        <v>6.579197689694923</v>
+        <v>6.840992730204849</v>
       </c>
       <c r="E5" t="n">
-        <v>14.27753724328618</v>
+        <v>14.05891400036713</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.826020022648074</v>
+        <v>1.768494565465461</v>
       </c>
       <c r="C6" t="n">
-        <v>7.084271016723648</v>
+        <v>6.334349099734157</v>
       </c>
       <c r="D6" t="n">
-        <v>6.934930478785168</v>
+        <v>7.172016425824553</v>
       </c>
       <c r="E6" t="n">
-        <v>15.84522151815689</v>
+        <v>15.27486009102417</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.06398550495769</v>
+        <v>1.987257682586522</v>
       </c>
       <c r="C7" t="n">
-        <v>8.217105188721604</v>
+        <v>7.171186640686309</v>
       </c>
       <c r="D7" t="n">
-        <v>7.338036685129417</v>
+        <v>7.596470537700587</v>
       </c>
       <c r="E7" t="n">
-        <v>17.61912737880871</v>
+        <v>16.75491486097342</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.274790296598106</v>
+        <v>1.202527431862898</v>
       </c>
       <c r="C8" t="n">
-        <v>5.802116048182052</v>
+        <v>4.927499571691897</v>
       </c>
       <c r="D8" t="n">
-        <v>5.562072433525385</v>
+        <v>5.894682205290792</v>
       </c>
       <c r="E8" t="n">
-        <v>12.63897877830554</v>
+        <v>12.02470920884559</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.590630436167326</v>
+        <v>1.492782656123995</v>
       </c>
       <c r="C9" t="n">
-        <v>7.152213305953605</v>
+        <v>6.177910290562575</v>
       </c>
       <c r="D9" t="n">
-        <v>6.023898025320944</v>
+        <v>6.560418042813256</v>
       </c>
       <c r="E9" t="n">
-        <v>14.76674176744188</v>
+        <v>14.23111098949983</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.923886800472846</v>
+        <v>1.809074666687395</v>
       </c>
       <c r="C10" t="n">
-        <v>8.652909542875539</v>
+        <v>7.67609109561901</v>
       </c>
       <c r="D10" t="n">
-        <v>6.524373109177526</v>
+        <v>7.162472699727719</v>
       </c>
       <c r="E10" t="n">
-        <v>17.10116945252591</v>
+        <v>16.64763846203412</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.263253797395729</v>
+        <v>2.118676438382137</v>
       </c>
       <c r="C11" t="n">
-        <v>10.27108186263754</v>
+        <v>9.340168208172313</v>
       </c>
       <c r="D11" t="n">
-        <v>6.983398584643968</v>
+        <v>7.833420007325778</v>
       </c>
       <c r="E11" t="n">
-        <v>19.51773424467724</v>
+        <v>19.29226465388023</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.598143785716809</v>
+        <v>2.42290823262493</v>
       </c>
       <c r="C12" t="n">
-        <v>11.99042653893419</v>
+        <v>11.15775192052079</v>
       </c>
       <c r="D12" t="n">
-        <v>7.479157448509535</v>
+        <v>8.460026339083962</v>
       </c>
       <c r="E12" t="n">
-        <v>22.06772777316054</v>
+        <v>22.04068649222968</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.906842613183938</v>
+        <v>2.703770528783529</v>
       </c>
       <c r="C13" t="n">
-        <v>13.73122430540141</v>
+        <v>13.01475896425617</v>
       </c>
       <c r="D13" t="n">
-        <v>7.901811857309659</v>
+        <v>9.163191341066632</v>
       </c>
       <c r="E13" t="n">
-        <v>24.53987877589501</v>
+        <v>24.88172083410633</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.66814642914801</v>
+        <v>1.559516045673101</v>
       </c>
       <c r="C14" t="n">
-        <v>9.662812509141062</v>
+        <v>9.043045000927094</v>
       </c>
       <c r="D14" t="n">
-        <v>6.020057287487357</v>
+        <v>6.969888373869103</v>
       </c>
       <c r="E14" t="n">
-        <v>17.35101622577643</v>
+        <v>17.5724494204693</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.698266448714302</v>
+        <v>1.573280148486641</v>
       </c>
       <c r="C15" t="n">
-        <v>10.4707025124428</v>
+        <v>10.05590428992148</v>
       </c>
       <c r="D15" t="n">
-        <v>6.00794252081695</v>
+        <v>7.088120249891547</v>
       </c>
       <c r="E15" t="n">
-        <v>18.17691148197406</v>
+        <v>18.71730468829967</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.952372207004504</v>
+        <v>1.797864753310142</v>
       </c>
       <c r="C16" t="n">
-        <v>12.38224383242768</v>
+        <v>12.01718094860351</v>
       </c>
       <c r="D16" t="n">
-        <v>6.445026416224674</v>
+        <v>7.655894399688606</v>
       </c>
       <c r="E16" t="n">
-        <v>20.77964245565686</v>
+        <v>21.47094010160225</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.555235625682585</v>
+        <v>1.42371088574464</v>
       </c>
       <c r="C17" t="n">
-        <v>11.38816537701553</v>
+        <v>11.22496945613859</v>
       </c>
       <c r="D17" t="n">
-        <v>5.969546368103859</v>
+        <v>7.160317976061857</v>
       </c>
       <c r="E17" t="n">
-        <v>18.91294737080198</v>
+        <v>19.80899831794508</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.763915917697287</v>
+        <v>1.597637309029004</v>
       </c>
       <c r="C18" t="n">
-        <v>13.29113603954234</v>
+        <v>13.18378192808295</v>
       </c>
       <c r="D18" t="n">
-        <v>6.362539974113856</v>
+        <v>7.634708284230958</v>
       </c>
       <c r="E18" t="n">
-        <v>21.41759193135348</v>
+        <v>22.41612752134291</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.756582262346563</v>
+        <v>1.576294113938679</v>
       </c>
       <c r="C19" t="n">
-        <v>14.22558313939854</v>
+        <v>14.16630521301611</v>
       </c>
       <c r="D19" t="n">
-        <v>6.43563109069503</v>
+        <v>7.753352494289186</v>
       </c>
       <c r="E19" t="n">
-        <v>22.41779649244013</v>
+        <v>23.49595182124398</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.940915211295944</v>
+        <v>1.72080737600381</v>
       </c>
       <c r="C20" t="n">
-        <v>16.29598105540759</v>
+        <v>16.27442187582233</v>
       </c>
       <c r="D20" t="n">
-        <v>6.861100910761515</v>
+        <v>8.235282624826901</v>
       </c>
       <c r="E20" t="n">
-        <v>25.09799717746505</v>
+        <v>26.23051187665304</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.14574865824124</v>
+        <v>1.009727513817845</v>
       </c>
       <c r="C21" t="n">
-        <v>11.94504212729545</v>
+        <v>11.90587039389601</v>
       </c>
       <c r="D21" t="n">
-        <v>5.720899127049268</v>
+        <v>6.916186774446803</v>
       </c>
       <c r="E21" t="n">
-        <v>18.81168991258596</v>
+        <v>19.83178468216065</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_97_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254562074061037</v>
+        <v>2.602622503318867</v>
       </c>
       <c r="C3" t="n">
-        <v>4.607937787946921</v>
+        <v>7.684656776779541</v>
       </c>
       <c r="D3" t="n">
-        <v>6.161973920809394</v>
+        <v>8.238618372078763</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02447378281735</v>
+        <v>18.52589765217717</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.387418974196815</v>
+        <v>1.119601797432853</v>
       </c>
       <c r="C4" t="n">
-        <v>5.079440726713631</v>
+        <v>4.443542020050074</v>
       </c>
       <c r="D4" t="n">
-        <v>6.442547025385615</v>
+        <v>5.779607445133608</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90940672629606</v>
+        <v>11.34275126261653</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.566587460014959</v>
+        <v>1.269077371154489</v>
       </c>
       <c r="C5" t="n">
-        <v>5.651333810147318</v>
+        <v>5.015631025270957</v>
       </c>
       <c r="D5" t="n">
-        <v>6.840992730204849</v>
+        <v>6.088761908597763</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05891400036713</v>
+        <v>12.37347030502321</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.768494565465461</v>
+        <v>1.441598233381281</v>
       </c>
       <c r="C6" t="n">
-        <v>6.334349099734157</v>
+        <v>5.71268569949441</v>
       </c>
       <c r="D6" t="n">
-        <v>7.172016425824553</v>
+        <v>6.51860184575082</v>
       </c>
       <c r="E6" t="n">
-        <v>15.27486009102417</v>
+        <v>13.67288577862651</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.987257682586522</v>
+        <v>1.612397476957413</v>
       </c>
       <c r="C7" t="n">
-        <v>7.171186640686309</v>
+        <v>6.563603455692192</v>
       </c>
       <c r="D7" t="n">
-        <v>7.596470537700587</v>
+        <v>6.931795960170811</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75491486097342</v>
+        <v>15.10779689282042</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.202527431862898</v>
+        <v>1.795493095449745</v>
       </c>
       <c r="C8" t="n">
-        <v>4.927499571691897</v>
+        <v>7.527719635014639</v>
       </c>
       <c r="D8" t="n">
-        <v>5.894682205290792</v>
+        <v>7.319018535349323</v>
       </c>
       <c r="E8" t="n">
-        <v>12.02470920884559</v>
+        <v>16.64223126581371</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.492782656123995</v>
+        <v>1.987293143371829</v>
       </c>
       <c r="C9" t="n">
-        <v>6.177910290562575</v>
+        <v>8.630900077154127</v>
       </c>
       <c r="D9" t="n">
-        <v>6.560418042813256</v>
+        <v>7.797850958954607</v>
       </c>
       <c r="E9" t="n">
-        <v>14.23111098949983</v>
+        <v>18.41604417948056</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.809074666687395</v>
+        <v>1.214981506344725</v>
       </c>
       <c r="C10" t="n">
-        <v>7.67609109561901</v>
+        <v>6.46593764232513</v>
       </c>
       <c r="D10" t="n">
-        <v>7.162472699727719</v>
+        <v>6.152740489716312</v>
       </c>
       <c r="E10" t="n">
-        <v>16.64763846203412</v>
+        <v>13.83365963838617</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.118676438382137</v>
+        <v>1.179353882157608</v>
       </c>
       <c r="C11" t="n">
-        <v>9.340168208172313</v>
+        <v>6.790915767384909</v>
       </c>
       <c r="D11" t="n">
-        <v>7.833420007325778</v>
+        <v>6.037394951944354</v>
       </c>
       <c r="E11" t="n">
-        <v>19.29226465388023</v>
+        <v>14.00766460148687</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.42290823262493</v>
+        <v>1.317034180201181</v>
       </c>
       <c r="C12" t="n">
-        <v>11.15775192052079</v>
+        <v>8.054523237520979</v>
       </c>
       <c r="D12" t="n">
-        <v>8.460026339083962</v>
+        <v>6.464504290676929</v>
       </c>
       <c r="E12" t="n">
-        <v>22.04068649222968</v>
+        <v>15.83606170839909</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.703770528783529</v>
+        <v>1.066001292225272</v>
       </c>
       <c r="C13" t="n">
-        <v>13.01475896425617</v>
+        <v>7.742837976376702</v>
       </c>
       <c r="D13" t="n">
-        <v>9.163191341066632</v>
+        <v>5.94142911385423</v>
       </c>
       <c r="E13" t="n">
-        <v>24.88172083410633</v>
+        <v>14.7502683824562</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.559516045673101</v>
+        <v>1.187728190074834</v>
       </c>
       <c r="C14" t="n">
-        <v>9.043045000927094</v>
+        <v>9.147463686750783</v>
       </c>
       <c r="D14" t="n">
-        <v>6.969888373869103</v>
+        <v>6.351917463953905</v>
       </c>
       <c r="E14" t="n">
-        <v>17.5724494204693</v>
+        <v>16.68710934077952</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.573280148486641</v>
+        <v>1.177419839180242</v>
       </c>
       <c r="C15" t="n">
-        <v>10.05590428992148</v>
+        <v>9.951014365199756</v>
       </c>
       <c r="D15" t="n">
-        <v>7.088120249891547</v>
+        <v>6.443072738293222</v>
       </c>
       <c r="E15" t="n">
-        <v>18.71730468829967</v>
+        <v>17.57150694267322</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.797864753310142</v>
+        <v>1.302396321930861</v>
       </c>
       <c r="C16" t="n">
-        <v>12.01718094860351</v>
+        <v>11.67898849944456</v>
       </c>
       <c r="D16" t="n">
-        <v>7.655894399688606</v>
+        <v>6.885644603367684</v>
       </c>
       <c r="E16" t="n">
-        <v>21.47094010160225</v>
+        <v>19.86702942474311</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.42371088574464</v>
+        <v>0.7820994911111792</v>
       </c>
       <c r="C17" t="n">
-        <v>11.22496945613859</v>
+        <v>8.843455692653716</v>
       </c>
       <c r="D17" t="n">
-        <v>7.160317976061857</v>
+        <v>5.743459689292861</v>
       </c>
       <c r="E17" t="n">
-        <v>19.80899831794508</v>
+        <v>15.36901487305776</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.597637309029004</v>
+        <v>0.6292315560829083</v>
       </c>
       <c r="C18" t="n">
-        <v>13.18378192808295</v>
+        <v>7.908233012111162</v>
       </c>
       <c r="D18" t="n">
-        <v>7.634708284230958</v>
+        <v>5.264131190171397</v>
       </c>
       <c r="E18" t="n">
-        <v>22.41612752134291</v>
+        <v>13.80159575836547</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.576294113938679</v>
+        <v>0.7397468951499716</v>
       </c>
       <c r="C19" t="n">
-        <v>14.16630521301611</v>
+        <v>9.775939297101422</v>
       </c>
       <c r="D19" t="n">
-        <v>7.753352494289186</v>
+        <v>5.807813251306238</v>
       </c>
       <c r="E19" t="n">
-        <v>23.49595182124398</v>
+        <v>16.32349944355763</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.72080737600381</v>
+        <v>0.8441361285425349</v>
       </c>
       <c r="C20" t="n">
-        <v>16.27442187582233</v>
+        <v>11.75010630314021</v>
       </c>
       <c r="D20" t="n">
-        <v>8.235282624826901</v>
+        <v>6.325429910893327</v>
       </c>
       <c r="E20" t="n">
-        <v>26.23051187665304</v>
+        <v>18.91967234257607</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.009727513817845</v>
+        <v>0.9410051745205678</v>
       </c>
       <c r="C21" t="n">
-        <v>11.90587039389601</v>
+        <v>13.76796108201797</v>
       </c>
       <c r="D21" t="n">
-        <v>6.916186774446803</v>
+        <v>6.921223140169588</v>
       </c>
       <c r="E21" t="n">
-        <v>19.83178468216065</v>
+        <v>21.63018939670813</v>
       </c>
     </row>
   </sheetData>
